--- a/tasks/xlsx/forte-finance-018-receivables-payables-consolidation/solution/往来款跨期整合.xlsx
+++ b/tasks/xlsx/forte-finance-018-receivables-payables-consolidation/solution/往来款跨期整合.xlsx
@@ -9819,101 +9819,101 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>【安途房车服务有限公司】</t>
+          <t>【圣龙供应链管理】</t>
         </is>
       </c>
       <c r="C2" s="3" t="n">
-        <v>20000</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>其他应付款\其他</t>
+          <t>其他应付款\租赁保证金</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>【安途房车服务有限公司】</t>
+          <t>【宇思智能】</t>
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>2000</v>
+        <v>15000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>合同负债</t>
+          <t>其他应付款\其他</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>【安途房车服务有限公司】</t>
+          <t>【宇思智能】</t>
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>240</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>应付账款\应付资产运营业务款</t>
+          <t>其他应付款\租赁保证金</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>【成都数点云管理服务部】</t>
+          <t>【安途房车服务有限公司】</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>130750.43</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>应付账款\应付资产运营业务款</t>
+          <t>其他应付款\其他</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>【达人星球文化传媒有限公司】</t>
+          <t>【安途房车服务有限公司】</t>
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>21090</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>预收账款\资产运营业务预收款</t>
+          <t>合同负债</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>【抖音支付科技有限公司】</t>
+          <t>【安途房车服务有限公司】</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>14910.5</v>
+        <v>240</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>应付账款\应付资产运营业务款</t>
+          <t>其他应付款\其他</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>【观山湖数微科技】</t>
+          <t>【小灵融传媒】</t>
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>246833.13</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9">
@@ -9924,26 +9924,26 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>【河南萌萌熊商贸】</t>
+          <t>【成都数点云管理服务部】</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>19948.97</v>
+        <v>130750.43</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>其他应付款\其他</t>
+          <t>应付账款\应付资产运营业务款</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>【河南萌萌熊商贸】</t>
+          <t>【扬帆文化传播中心】</t>
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>4000</v>
+        <v>474600.33</v>
       </c>
     </row>
     <row r="11">
@@ -9954,86 +9954,86 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>【河南萌萌熊商贸】</t>
+          <t>【扬帆文化传播中心】</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>2155.74</v>
+        <v>97618.48</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>应付账款\应付其他</t>
+          <t>其他应付款\租赁保证金</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>【黄杉文化传播有限公司】</t>
+          <t>【扬帆文化传播中心】</t>
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>2201834.86</v>
+        <v>60000</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>其他应付款\租赁保证金</t>
+          <t>其他应付款\其他</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>【金华市蓝网智能科技有限公司】</t>
+          <t>【扬帆文化传播中心】</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>20000</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>应付账款\应付资产运营业务款</t>
+          <t>预收账款\资产运营业务预收款</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>【金华市蓝网智能科技有限公司】</t>
+          <t>【抖音支付科技有限公司】</t>
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>11074.45</v>
+        <v>14910.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>应付账款\应付其他</t>
+          <t>应付账款\应付资产运营业务款</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>【金华市蓝网智能科技有限公司】</t>
+          <t>【河南萌萌熊商贸】</t>
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>2868.93</v>
+        <v>19948.97</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>应付账款\应付资产运营业务款</t>
+          <t>其他应付款\其他</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>【肯德基成都腾讯大厦餐厅】</t>
+          <t>【河南萌萌熊商贸】</t>
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>14207</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="17">
@@ -10044,26 +10044,26 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>【肯德基成都腾讯大厦餐厅】</t>
+          <t>【河南萌萌熊商贸】</t>
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>13956</v>
+        <v>2155.74</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>其他应付款\租赁保证金</t>
+          <t>其他应付款\其他</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>【肯德基成都腾讯大厦餐厅】</t>
+          <t>【深域蓝海游乐中心】</t>
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>10000</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="19">
@@ -10074,206 +10074,206 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>【绵阳税同律师事务所】</t>
+          <t>【盛装舞步马术俱乐部】</t>
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>156000</v>
+        <v>17333.54</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>应付账款\应付资产运营业务款</t>
+          <t>应付账款\应付其他</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>【魔典引擎】</t>
+          <t>【盛装舞步马术俱乐部】</t>
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>341677.91</v>
+        <v>14406.19</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>其他应付款\其他</t>
+          <t>应付账款\应付资产运营业务款</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>【魔典引擎】</t>
+          <t>【绵阳税同律师事务所】</t>
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>20000</v>
+        <v>156000</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>其他应付款\其他</t>
+          <t>应付账款\应付资产运营业务款</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>【深域蓝海游乐中心】</t>
+          <t>【肯德基成都腾讯大厦餐厅】</t>
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>20000</v>
+        <v>14207</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>其他应付款\租赁保证金</t>
+          <t>应付账款\应付其他</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>【圣龙供应链管理】</t>
+          <t>【肯德基成都腾讯大厦餐厅】</t>
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>10000</v>
+        <v>13956</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>应付账款\应付资产运营业务款</t>
+          <t>其他应付款\租赁保证金</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>【盛装舞步马术俱乐部】</t>
+          <t>【肯德基成都腾讯大厦餐厅】</t>
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>17333.54</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>应付账款\应付其他</t>
+          <t>应付账款\应付资产运营业务款</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>【盛装舞步马术俱乐部】</t>
+          <t>【观山湖数微科技】</t>
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>14406.19</v>
+        <v>246833.13</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>其他应付款\其他</t>
+          <t>应付账款\应付资产运营业务款</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>【小灵融传媒】</t>
+          <t>【达人星球文化传媒有限公司】</t>
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>100</v>
+        <v>21090</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>应付账款\应付资产运营业务款</t>
+          <t>其他应付款\租赁保证金</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>【扬帆文化传播中心】</t>
+          <t>【金华市蓝网智能科技有限公司】</t>
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>474600.33</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>应付账款\应付其他</t>
+          <t>应付账款\应付资产运营业务款</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>【扬帆文化传播中心】</t>
+          <t>【金华市蓝网智能科技有限公司】</t>
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>97618.48</v>
+        <v>11074.45</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>其他应付款\租赁保证金</t>
+          <t>应付账款\应付其他</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>【扬帆文化传播中心】</t>
+          <t>【金华市蓝网智能科技有限公司】</t>
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>60000</v>
+        <v>2868.93</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>其他应付款\其他</t>
+          <t>应付账款\应付资产运营业务款</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>【扬帆文化传播中心】</t>
+          <t>【魔典引擎】</t>
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>10000</v>
+        <v>341677.91</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>其他应付款\租赁保证金</t>
+          <t>其他应付款\其他</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>【宇思智能】</t>
+          <t>【魔典引擎】</t>
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>15000</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>其他应付款\其他</t>
+          <t>应付账款\应付其他</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>【宇思智能】</t>
+          <t>【黄杉文化传播有限公司】</t>
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>12000</v>
+        <v>2201834.86</v>
       </c>
     </row>
   </sheetData>
@@ -10328,31 +10328,31 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>内部往来</t>
+          <t>其他应收款\其他应收往来</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>【黄杉文化传播有限公司】</t>
+          <t>【绵阳长城发展融资担保有限公司】</t>
         </is>
       </c>
       <c r="C2" s="3" t="n">
-        <v>3292891.47</v>
+        <v>1700000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>其他应收款\其他应收往来</t>
+          <t>内部往来</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>【绵阳长城发展融资担保有限公司】</t>
+          <t>【黄杉文化传播有限公司】</t>
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>1700000</v>
+        <v>3292891.47</v>
       </c>
     </row>
   </sheetData>
@@ -10425,22 +10425,22 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>内部往来</t>
+          <t>其他应收款\其他应收往来</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>【黄杉文化传播有限公司】</t>
+          <t>【绵阳长城发展融资担保有限公司】</t>
         </is>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1853858.43</v>
+        <v>1500000</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>4672887.5</v>
+        <v>1500000</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>3292891.47</v>
+        <v>1700000</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
@@ -10451,22 +10451,22 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>其他应收款\其他应收往来</t>
+          <t>内部往来</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>【绵阳长城发展融资担保有限公司】</t>
+          <t>【黄杉文化传播有限公司】</t>
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>1500000</v>
+        <v>1853858.43</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>1500000</v>
+        <v>4672887.5</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>1700000</v>
+        <v>3292891.47</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
